--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132562598</v>
       </c>
       <c r="B3" t="n">
-        <v>57942</v>
+        <v>57943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,6 +907,229 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132663314</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92358</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 18214, Granebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574280</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6407552</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov granlåga med ullticka</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132663290</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 18214, Granebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>574280</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6407552</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132562598</v>
       </c>
       <c r="B3" t="n">
-        <v>57943</v>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92358</v>
+        <v>92368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>132663290</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>132663290</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132562598</v>
       </c>
       <c r="B3" t="n">
-        <v>57947</v>
+        <v>57948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>132663290</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>132663290</v>
       </c>
       <c r="B5" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132562649</v>
       </c>
       <c r="B2" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>132663290</v>
       </c>
       <c r="B5" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 18214-2026 artfynd.xlsx
+++ b/artfynd/A 18214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132562649</v>
+        <v>132663258</v>
       </c>
       <c r="B2" t="n">
-        <v>101338</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hulthorva, Sm</t>
+          <t>A 18214, Granebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574280</v>
+        <v>574276</v>
       </c>
       <c r="R2" t="n">
-        <v>6407517</v>
+        <v>6407573</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,44 +772,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132562598</v>
+        <v>132663290</v>
       </c>
       <c r="B3" t="n">
-        <v>57952</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,31 +817,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hulthorva, Sm</t>
+          <t>A 18214, Granebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574288</v>
+        <v>574280</v>
       </c>
       <c r="R3" t="n">
-        <v>6407520</v>
+        <v>6407552</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,18 +874,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -913,11 +896,11 @@
         <v>132663314</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1024,32 +1007,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132663290</v>
+        <v>132562598</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>57969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1057,26 +1040,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 18214, Granebo, Sm</t>
+          <t>Hulthorva, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574280</v>
+        <v>574288</v>
       </c>
       <c r="R5" t="n">
-        <v>6407552</v>
+        <v>6407520</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,12 +1088,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,22 +1112,243 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132663439</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 18214, Granebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>574287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6407571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132562649</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hulthorva, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>574280</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6407517</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ante Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
